--- a/PSO_histreet/v2/output/reports/PSO_Pricing_Strategy_Workbook.xlsx
+++ b/PSO_histreet/v2/output/reports/PSO_Pricing_Strategy_Workbook.xlsx
@@ -813,6 +813,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="8" customHeight="1"/>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1496,7 +1497,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -1520,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1544,7 +1545,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -1568,7 +1569,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -1592,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$19</f>
+        <f>$H$19</f>
         <v/>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -1616,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$20</f>
+        <f>$H$20</f>
         <v/>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -1640,7 +1641,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -1664,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$14</f>
+        <f>$H$14</f>
         <v/>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -1688,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$18</f>
+        <f>$H$18</f>
         <v/>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -1712,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$19</f>
+        <f>$H$19</f>
         <v/>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -1736,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$20</f>
+        <f>$H$20</f>
         <v/>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -1760,7 +1761,7 @@
         <v>3</v>
       </c>
       <c r="D35" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$14</f>
+        <f>$H$14</f>
         <v/>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -1784,7 +1785,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$18</f>
+        <f>$H$18</f>
         <v/>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -1808,7 +1809,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$19</f>
+        <f>$H$19</f>
         <v/>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -1832,7 +1833,7 @@
         <v>3</v>
       </c>
       <c r="D38" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$20</f>
+        <f>$H$20</f>
         <v/>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -1856,7 +1857,7 @@
         <v>4</v>
       </c>
       <c r="D39" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$14</f>
+        <f>$H$14</f>
         <v/>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -1880,7 +1881,7 @@
         <v>4</v>
       </c>
       <c r="D40" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$18</f>
+        <f>$H$18</f>
         <v/>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -1904,7 +1905,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$19</f>
+        <f>$H$19</f>
         <v/>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -1928,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$20</f>
+        <f>$H$20</f>
         <v/>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -1952,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1976,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -2000,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -2024,7 +2025,7 @@
         <v>3</v>
       </c>
       <c r="D46" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -2048,7 +2049,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -2072,7 +2073,7 @@
         <v>3</v>
       </c>
       <c r="D48" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -2096,7 +2097,7 @@
         <v>4</v>
       </c>
       <c r="D49" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -2120,7 +2121,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -2144,7 +2145,7 @@
         <v>4</v>
       </c>
       <c r="D51" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -2168,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -2192,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -2216,7 +2217,7 @@
         <v>0.7</v>
       </c>
       <c r="D54" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -2240,7 +2241,7 @@
         <v>0.7</v>
       </c>
       <c r="D55" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -2264,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -2288,7 +2289,7 @@
         <v>4</v>
       </c>
       <c r="D57" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -2312,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="D58" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -2336,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -2360,7 +2361,7 @@
         <v>4</v>
       </c>
       <c r="D60" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -2384,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -2408,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -2432,7 +2433,7 @@
         <v>4</v>
       </c>
       <c r="D63" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -2456,7 +2457,7 @@
         <v>4</v>
       </c>
       <c r="D64" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -2480,7 +2481,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$15</f>
+        <f>$H$15</f>
         <v/>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -2504,7 +2505,7 @@
         <v>4</v>
       </c>
       <c r="D66" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -2528,7 +2529,7 @@
         <v>4</v>
       </c>
       <c r="D67" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$16</f>
+        <f>$H$16</f>
         <v/>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -2552,7 +2553,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="26">
-        <f>'F7 â€“ Base Oil Floor'!$H$17</f>
+        <f>$H$17</f>
         <v/>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -4527,6 +4528,7 @@
         <v/>
       </c>
     </row>
+    <row r="58"/>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="31" t="inlineStr">
         <is>
@@ -24555,6 +24557,7 @@
         <v/>
       </c>
     </row>
+    <row r="65"/>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
@@ -25435,7 +25438,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$14</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="F32" s="26">
@@ -25467,7 +25470,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$18</f>
+        <f>$E$18</f>
         <v/>
       </c>
       <c r="F33" s="26">
@@ -25499,7 +25502,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$15</f>
+        <f>$E$15</f>
         <v/>
       </c>
       <c r="F34" s="26">
@@ -25531,7 +25534,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$19</f>
+        <f>$E$19</f>
         <v/>
       </c>
       <c r="F35" s="26">
@@ -25563,7 +25566,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$25</f>
+        <f>$E$25</f>
         <v/>
       </c>
       <c r="F36" s="26">
@@ -25595,7 +25598,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$28</f>
+        <f>$E$28</f>
         <v/>
       </c>
       <c r="F37" s="26">
@@ -25627,7 +25630,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$12</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="F38" s="26">
@@ -25659,7 +25662,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$6</f>
+        <f>$E$6</f>
         <v/>
       </c>
       <c r="F39" s="26">
@@ -25691,7 +25694,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$20</f>
+        <f>$E$20</f>
         <v/>
       </c>
       <c r="F40" s="26">
@@ -25723,7 +25726,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$23</f>
+        <f>$E$23</f>
         <v/>
       </c>
       <c r="F41" s="26">
@@ -25755,7 +25758,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$26</f>
+        <f>$E$26</f>
         <v/>
       </c>
       <c r="F42" s="26">
@@ -25787,7 +25790,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$7</f>
+        <f>$E$7</f>
         <v/>
       </c>
       <c r="F43" s="26">
@@ -25819,7 +25822,7 @@
         <v>3</v>
       </c>
       <c r="E44" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$21</f>
+        <f>$E$21</f>
         <v/>
       </c>
       <c r="F44" s="26">
@@ -25851,7 +25854,7 @@
         <v>3</v>
       </c>
       <c r="E45" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$24</f>
+        <f>$E$24</f>
         <v/>
       </c>
       <c r="F45" s="26">
@@ -25883,7 +25886,7 @@
         <v>3</v>
       </c>
       <c r="E46" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$27</f>
+        <f>$E$27</f>
         <v/>
       </c>
       <c r="F46" s="26">
@@ -25915,7 +25918,7 @@
         <v>4</v>
       </c>
       <c r="E47" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$8</f>
+        <f>$E$8</f>
         <v/>
       </c>
       <c r="F47" s="26">
@@ -25947,7 +25950,7 @@
         <v>4</v>
       </c>
       <c r="E48" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$22</f>
+        <f>$E$22</f>
         <v/>
       </c>
       <c r="F48" s="26">
@@ -25979,7 +25982,7 @@
         <v>4</v>
       </c>
       <c r="E49" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$25</f>
+        <f>$E$25</f>
         <v/>
       </c>
       <c r="F49" s="26">
@@ -26011,7 +26014,7 @@
         <v>4</v>
       </c>
       <c r="E50" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$28</f>
+        <f>$E$28</f>
         <v/>
       </c>
       <c r="F50" s="26">
@@ -26043,7 +26046,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$10</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="F51" s="26">
@@ -26075,7 +26078,7 @@
         <v>1</v>
       </c>
       <c r="E52" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$13</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="F52" s="26">
@@ -26107,7 +26110,7 @@
         <v>1</v>
       </c>
       <c r="E53" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$17</f>
+        <f>$E$17</f>
         <v/>
       </c>
       <c r="F53" s="26">
@@ -26139,7 +26142,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$11</f>
+        <f>$E$11</f>
         <v/>
       </c>
       <c r="F54" s="26">
@@ -26171,7 +26174,7 @@
         <v>3</v>
       </c>
       <c r="E55" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$14</f>
+        <f>$E$14</f>
         <v/>
       </c>
       <c r="F55" s="26">
@@ -26203,7 +26206,7 @@
         <v>3</v>
       </c>
       <c r="E56" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$18</f>
+        <f>$E$18</f>
         <v/>
       </c>
       <c r="F56" s="26">
@@ -26235,7 +26238,7 @@
         <v>4</v>
       </c>
       <c r="E57" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$12</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="F57" s="26">
@@ -26267,7 +26270,7 @@
         <v>4</v>
       </c>
       <c r="E58" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$15</f>
+        <f>$E$15</f>
         <v/>
       </c>
       <c r="F58" s="26">
@@ -26299,7 +26302,7 @@
         <v>4</v>
       </c>
       <c r="E59" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$19</f>
+        <f>$E$19</f>
         <v/>
       </c>
       <c r="F59" s="26">
@@ -26331,7 +26334,7 @@
         <v>1</v>
       </c>
       <c r="E60" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$10</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="F60" s="26">
@@ -26363,7 +26366,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$17</f>
+        <f>$E$17</f>
         <v/>
       </c>
       <c r="F61" s="26">
@@ -26395,7 +26398,7 @@
         <v>0.7</v>
       </c>
       <c r="E62" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$9</f>
+        <f>$E$9</f>
         <v/>
       </c>
       <c r="F62" s="26">
@@ -26427,7 +26430,7 @@
         <v>0.7</v>
       </c>
       <c r="E63" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$16</f>
+        <f>$E$16</f>
         <v/>
       </c>
       <c r="F63" s="26">
@@ -26459,7 +26462,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$10</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="F64" s="26">
@@ -26491,7 +26494,7 @@
         <v>4</v>
       </c>
       <c r="E65" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$15</f>
+        <f>$E$15</f>
         <v/>
       </c>
       <c r="F65" s="26">
@@ -26523,7 +26526,7 @@
         <v>4</v>
       </c>
       <c r="E66" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$19</f>
+        <f>$E$19</f>
         <v/>
       </c>
       <c r="F66" s="26">
@@ -26555,7 +26558,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$13</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="F67" s="26">
@@ -26587,7 +26590,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$15</f>
+        <f>$E$15</f>
         <v/>
       </c>
       <c r="F68" s="26">
@@ -26619,7 +26622,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$10</f>
+        <f>$E$10</f>
         <v/>
       </c>
       <c r="F69" s="26">
@@ -26651,7 +26654,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$13</f>
+        <f>$E$13</f>
         <v/>
       </c>
       <c r="F70" s="26">
@@ -26683,7 +26686,7 @@
         <v>4</v>
       </c>
       <c r="E71" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$12</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="F71" s="26">
@@ -26715,7 +26718,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$15</f>
+        <f>$E$15</f>
         <v/>
       </c>
       <c r="F72" s="26">
@@ -26747,7 +26750,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$12</f>
+        <f>$E$12</f>
         <v/>
       </c>
       <c r="F73" s="26">
@@ -26779,7 +26782,7 @@
         <v>4</v>
       </c>
       <c r="E74" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$15</f>
+        <f>$E$15</f>
         <v/>
       </c>
       <c r="F74" s="26">
@@ -26811,7 +26814,7 @@
         <v>4</v>
       </c>
       <c r="E75" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$15</f>
+        <f>$E$15</f>
         <v/>
       </c>
       <c r="F75" s="26">
@@ -26843,7 +26846,7 @@
         <v>4</v>
       </c>
       <c r="E76" s="26">
-        <f>'F2 â€“ Market Ref Price'!$E$19</f>
+        <f>$E$19</f>
         <v/>
       </c>
       <c r="F76" s="26">
@@ -27347,7 +27350,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F30" s="12" t="n">
@@ -27378,7 +27381,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F31" s="12" t="n">
@@ -27409,7 +27412,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F32" s="12" t="n">
@@ -27440,7 +27443,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F33" s="12" t="n">
@@ -27471,7 +27474,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$25</f>
+        <f>$B$25</f>
         <v/>
       </c>
       <c r="F34" s="12" t="n">
@@ -27502,7 +27505,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$26</f>
+        <f>$B$26</f>
         <v/>
       </c>
       <c r="F35" s="12" t="n">
@@ -27533,7 +27536,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F36" s="12" t="n">
@@ -27564,7 +27567,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$20</f>
+        <f>$B$20</f>
         <v/>
       </c>
       <c r="F37" s="12" t="n">
@@ -27595,7 +27598,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$24</f>
+        <f>$B$24</f>
         <v/>
       </c>
       <c r="F38" s="12" t="n">
@@ -27626,7 +27629,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$25</f>
+        <f>$B$25</f>
         <v/>
       </c>
       <c r="F39" s="12" t="n">
@@ -27657,7 +27660,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$26</f>
+        <f>$B$26</f>
         <v/>
       </c>
       <c r="F40" s="12" t="n">
@@ -27688,7 +27691,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$20</f>
+        <f>$B$20</f>
         <v/>
       </c>
       <c r="F41" s="12" t="n">
@@ -27719,7 +27722,7 @@
         <v>3</v>
       </c>
       <c r="E42" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$24</f>
+        <f>$B$24</f>
         <v/>
       </c>
       <c r="F42" s="12" t="n">
@@ -27750,7 +27753,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$25</f>
+        <f>$B$25</f>
         <v/>
       </c>
       <c r="F43" s="12" t="n">
@@ -27781,7 +27784,7 @@
         <v>3</v>
       </c>
       <c r="E44" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$26</f>
+        <f>$B$26</f>
         <v/>
       </c>
       <c r="F44" s="12" t="n">
@@ -27812,7 +27815,7 @@
         <v>4</v>
       </c>
       <c r="E45" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$20</f>
+        <f>$B$20</f>
         <v/>
       </c>
       <c r="F45" s="12" t="n">
@@ -27843,7 +27846,7 @@
         <v>4</v>
       </c>
       <c r="E46" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$24</f>
+        <f>$B$24</f>
         <v/>
       </c>
       <c r="F46" s="12" t="n">
@@ -27874,7 +27877,7 @@
         <v>4</v>
       </c>
       <c r="E47" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$25</f>
+        <f>$B$25</f>
         <v/>
       </c>
       <c r="F47" s="12" t="n">
@@ -27905,7 +27908,7 @@
         <v>4</v>
       </c>
       <c r="E48" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$26</f>
+        <f>$B$26</f>
         <v/>
       </c>
       <c r="F48" s="12" t="n">
@@ -27936,7 +27939,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F49" s="12" t="n">
@@ -27967,7 +27970,7 @@
         <v>1</v>
       </c>
       <c r="E50" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F50" s="12" t="n">
@@ -27998,7 +28001,7 @@
         <v>1</v>
       </c>
       <c r="E51" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F51" s="12" t="n">
@@ -28029,7 +28032,7 @@
         <v>3</v>
       </c>
       <c r="E52" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F52" s="12" t="n">
@@ -28060,7 +28063,7 @@
         <v>3</v>
       </c>
       <c r="E53" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F53" s="12" t="n">
@@ -28091,7 +28094,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F54" s="12" t="n">
@@ -28122,7 +28125,7 @@
         <v>4</v>
       </c>
       <c r="E55" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F55" s="12" t="n">
@@ -28153,7 +28156,7 @@
         <v>4</v>
       </c>
       <c r="E56" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F56" s="12" t="n">
@@ -28184,7 +28187,7 @@
         <v>4</v>
       </c>
       <c r="E57" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F57" s="12" t="n">
@@ -28215,7 +28218,7 @@
         <v>1</v>
       </c>
       <c r="E58" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F58" s="12" t="n">
@@ -28246,7 +28249,7 @@
         <v>1</v>
       </c>
       <c r="E59" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F59" s="12" t="n">
@@ -28277,7 +28280,7 @@
         <v>0.7</v>
       </c>
       <c r="E60" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F60" s="12" t="n">
@@ -28308,7 +28311,7 @@
         <v>0.7</v>
       </c>
       <c r="E61" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F61" s="12" t="n">
@@ -28339,7 +28342,7 @@
         <v>1</v>
       </c>
       <c r="E62" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F62" s="12" t="n">
@@ -28370,7 +28373,7 @@
         <v>4</v>
       </c>
       <c r="E63" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F63" s="12" t="n">
@@ -28401,7 +28404,7 @@
         <v>4</v>
       </c>
       <c r="E64" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F64" s="12" t="n">
@@ -28432,7 +28435,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F65" s="12" t="n">
@@ -28463,7 +28466,7 @@
         <v>4</v>
       </c>
       <c r="E66" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F66" s="12" t="n">
@@ -28494,7 +28497,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F67" s="12" t="n">
@@ -28525,7 +28528,7 @@
         <v>1</v>
       </c>
       <c r="E68" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F68" s="12" t="n">
@@ -28556,7 +28559,7 @@
         <v>4</v>
       </c>
       <c r="E69" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F69" s="12" t="n">
@@ -28587,7 +28590,7 @@
         <v>4</v>
       </c>
       <c r="E70" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F70" s="12" t="n">
@@ -28618,7 +28621,7 @@
         <v>4</v>
       </c>
       <c r="E71" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$21</f>
+        <f>$B$21</f>
         <v/>
       </c>
       <c r="F71" s="12" t="n">
@@ -28649,7 +28652,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F72" s="12" t="n">
@@ -28680,7 +28683,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$22</f>
+        <f>$B$22</f>
         <v/>
       </c>
       <c r="F73" s="12" t="n">
@@ -28711,7 +28714,7 @@
         <v>4</v>
       </c>
       <c r="E74" s="26">
-        <f>'F3 â€“ Pack Architecture'!$B$23</f>
+        <f>$B$23</f>
         <v/>
       </c>
       <c r="F74" s="12" t="n">
@@ -31391,6 +31394,7 @@
         <v/>
       </c>
     </row>
+    <row r="81"/>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="31" t="inlineStr">
         <is>
@@ -31778,11 +31782,11 @@
         </is>
       </c>
       <c r="E23" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F23" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$19</f>
+        <f>$C$19</f>
         <v/>
       </c>
       <c r="G23" s="30">
@@ -31812,11 +31816,11 @@
         </is>
       </c>
       <c r="E24" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F24" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$19</f>
+        <f>$C$19</f>
         <v/>
       </c>
       <c r="G24" s="30">
@@ -31846,11 +31850,11 @@
         </is>
       </c>
       <c r="E25" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F25" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$19</f>
+        <f>$C$19</f>
         <v/>
       </c>
       <c r="G25" s="30">
@@ -31880,11 +31884,11 @@
         </is>
       </c>
       <c r="E26" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F26" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$19</f>
+        <f>$C$19</f>
         <v/>
       </c>
       <c r="G26" s="30">
@@ -31914,11 +31918,11 @@
         </is>
       </c>
       <c r="E27" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$8</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="F27" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$17</f>
+        <f>$C$17</f>
         <v/>
       </c>
       <c r="G27" s="30">
@@ -31948,11 +31952,11 @@
         </is>
       </c>
       <c r="E28" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$9</f>
+        <f>$B$9</f>
         <v/>
       </c>
       <c r="F28" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$17</f>
+        <f>$C$17</f>
         <v/>
       </c>
       <c r="G28" s="30">
@@ -31982,11 +31986,11 @@
         </is>
       </c>
       <c r="E29" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F29" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$17</f>
+        <f>$C$17</f>
         <v/>
       </c>
       <c r="G29" s="30">
@@ -32016,11 +32020,11 @@
         </is>
       </c>
       <c r="E30" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$6</f>
+        <f>$B$6</f>
         <v/>
       </c>
       <c r="F30" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G30" s="30">
@@ -32050,11 +32054,11 @@
         </is>
       </c>
       <c r="E31" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$7</f>
+        <f>$B$7</f>
         <v/>
       </c>
       <c r="F31" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G31" s="30">
@@ -32084,11 +32088,11 @@
         </is>
       </c>
       <c r="E32" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$8</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="F32" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G32" s="30">
@@ -32118,11 +32122,11 @@
         </is>
       </c>
       <c r="E33" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$9</f>
+        <f>$B$9</f>
         <v/>
       </c>
       <c r="F33" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G33" s="30">
@@ -32152,11 +32156,11 @@
         </is>
       </c>
       <c r="E34" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$6</f>
+        <f>$B$6</f>
         <v/>
       </c>
       <c r="F34" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G34" s="30">
@@ -32186,11 +32190,11 @@
         </is>
       </c>
       <c r="E35" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$7</f>
+        <f>$B$7</f>
         <v/>
       </c>
       <c r="F35" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G35" s="30">
@@ -32220,11 +32224,11 @@
         </is>
       </c>
       <c r="E36" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$8</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="F36" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G36" s="30">
@@ -32254,11 +32258,11 @@
         </is>
       </c>
       <c r="E37" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$9</f>
+        <f>$B$9</f>
         <v/>
       </c>
       <c r="F37" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G37" s="30">
@@ -32288,11 +32292,11 @@
         </is>
       </c>
       <c r="E38" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$6</f>
+        <f>$B$6</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G38" s="30">
@@ -32322,11 +32326,11 @@
         </is>
       </c>
       <c r="E39" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$7</f>
+        <f>$B$7</f>
         <v/>
       </c>
       <c r="F39" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G39" s="30">
@@ -32356,11 +32360,11 @@
         </is>
       </c>
       <c r="E40" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$8</f>
+        <f>$B$8</f>
         <v/>
       </c>
       <c r="F40" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G40" s="30">
@@ -32390,11 +32394,11 @@
         </is>
       </c>
       <c r="E41" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$9</f>
+        <f>$B$9</f>
         <v/>
       </c>
       <c r="F41" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G41" s="30">
@@ -32424,11 +32428,11 @@
         </is>
       </c>
       <c r="E42" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F42" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G42" s="30">
@@ -32458,11 +32462,11 @@
         </is>
       </c>
       <c r="E43" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F43" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G43" s="30">
@@ -32492,11 +32496,11 @@
         </is>
       </c>
       <c r="E44" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F44" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G44" s="30">
@@ -32526,11 +32530,11 @@
         </is>
       </c>
       <c r="E45" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F45" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G45" s="30">
@@ -32560,11 +32564,11 @@
         </is>
       </c>
       <c r="E46" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F46" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G46" s="30">
@@ -32594,11 +32598,11 @@
         </is>
       </c>
       <c r="E47" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F47" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G47" s="30">
@@ -32628,11 +32632,11 @@
         </is>
       </c>
       <c r="E48" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F48" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G48" s="30">
@@ -32662,11 +32666,11 @@
         </is>
       </c>
       <c r="E49" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F49" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G49" s="30">
@@ -32696,11 +32700,11 @@
         </is>
       </c>
       <c r="E50" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F50" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G50" s="30">
@@ -32730,11 +32734,11 @@
         </is>
       </c>
       <c r="E51" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F51" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G51" s="30">
@@ -32764,11 +32768,11 @@
         </is>
       </c>
       <c r="E52" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F52" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G52" s="30">
@@ -32798,11 +32802,11 @@
         </is>
       </c>
       <c r="E53" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F53" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G53" s="30">
@@ -32832,11 +32836,11 @@
         </is>
       </c>
       <c r="E54" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F54" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G54" s="30">
@@ -32866,11 +32870,11 @@
         </is>
       </c>
       <c r="E55" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F55" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$17</f>
+        <f>$C$17</f>
         <v/>
       </c>
       <c r="G55" s="30">
@@ -32900,11 +32904,11 @@
         </is>
       </c>
       <c r="E56" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F56" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G56" s="30">
@@ -32934,11 +32938,11 @@
         </is>
       </c>
       <c r="E57" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F57" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$18</f>
+        <f>$C$18</f>
         <v/>
       </c>
       <c r="G57" s="30">
@@ -32968,11 +32972,11 @@
         </is>
       </c>
       <c r="E58" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F58" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$17</f>
+        <f>$C$17</f>
         <v/>
       </c>
       <c r="G58" s="30">
@@ -33002,11 +33006,11 @@
         </is>
       </c>
       <c r="E59" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F59" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$17</f>
+        <f>$C$17</f>
         <v/>
       </c>
       <c r="G59" s="30">
@@ -33036,11 +33040,11 @@
         </is>
       </c>
       <c r="E60" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F60" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G60" s="30">
@@ -33070,11 +33074,11 @@
         </is>
       </c>
       <c r="E61" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F61" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G61" s="30">
@@ -33104,11 +33108,11 @@
         </is>
       </c>
       <c r="E62" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F62" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G62" s="30">
@@ -33138,11 +33142,11 @@
         </is>
       </c>
       <c r="E63" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F63" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G63" s="30">
@@ -33172,11 +33176,11 @@
         </is>
       </c>
       <c r="E64" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$10</f>
+        <f>$B$10</f>
         <v/>
       </c>
       <c r="F64" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G64" s="30">
@@ -33206,11 +33210,11 @@
         </is>
       </c>
       <c r="E65" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F65" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$16</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="G65" s="30">
@@ -33240,11 +33244,11 @@
         </is>
       </c>
       <c r="E66" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$11</f>
+        <f>$B$11</f>
         <v/>
       </c>
       <c r="F66" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$19</f>
+        <f>$C$19</f>
         <v/>
       </c>
       <c r="G66" s="30">
@@ -33274,11 +33278,11 @@
         </is>
       </c>
       <c r="E67" s="26">
-        <f>'F5 â€“ Spec Premium'!$B$12</f>
+        <f>$B$12</f>
         <v/>
       </c>
       <c r="F67" s="32">
-        <f>'F5 â€“ Spec Premium'!$C$19</f>
+        <f>$C$19</f>
         <v/>
       </c>
       <c r="G67" s="30">
@@ -35639,6 +35643,7 @@
         <v/>
       </c>
     </row>
+    <row r="63"/>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>

--- a/PSO_histreet/v2/output/reports/PSO_Pricing_Strategy_Workbook.xlsx
+++ b/PSO_histreet/v2/output/reports/PSO_Pricing_Strategy_Workbook.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,8 +93,19 @@
       <color rgb="002980B9"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00111111"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -146,6 +157,21 @@
         <fgColor rgb="00FEFEFE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4FAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9ED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -173,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -273,6 +299,24 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -813,7 +857,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="8" customHeight="1"/>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1016,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2562,12 +2605,73 @@
         </is>
       </c>
     </row>
+    <row r="70" ht="10" customHeight="1"/>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="104" customHeight="1">
+      <c r="A72" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Takes the base oil import parity cost for the grade's required group (Group I: Rs 280/L, Group II: Rs 420/L, Group III: Rs 680/L).
+  •  Adds the grade-specific additive package cost and a fixed blending/overhead allocation of Rs 50/L.
+  •  Multiplies total manufacturing cost by 2.8x - the standard retail lubricants markup in Pakistan (equivalent to approximately 64% gross margin).
+  •  Formula: F7 Floor = (Base_Oil_Cost + Additive_Cost + Rs 50) x 2.8
+  •  F7 is a standalone sanity check and audit tool, not a synthesis input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="5" customHeight="1"/>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="117" customHeight="1">
+      <c r="A75" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Base oil is the primary raw material in any lubricant (55-75% of total product cost). Its price tracks crude oil with a 6-8 week lag, creating predictable cost movements.
+  •  The 2.8x markup is the industry standard for retail lubricants in Pakistan: derived from distributor margin (15%), dealer/pump margin (8%), PSO overhead (12%), and net profit target (10%).
+  •  F7 provides an independent floor that does not depend on competitor data (like F2) or margin targets (like F4). Even if competitive data is stale or targets are mis-set, F7 catches structural underpricing.
+  •  F7 is especially valuable during crude oil price shocks: when base oil import costs spike, F7 immediately shows which PSO products are now priced below manufacturing cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="5" customHeight="1"/>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="117" customHeight="1">
+      <c r="A78" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Any PSO SKU priced below its F7 floor is being sold at a structural loss. This should trigger an immediate price revision or product exit decision.
+  •  If F7 &gt; F4 for any SKU, the F4 margin target is set too low - revise the margin assumption upward for that tier before the next pricing cycle.
+  •  Monitor base oil import prices monthly (PARCO, NRL, and Korean import indices). A 10% crude oil increase typically translates to 8-12% increase in F7 floor values within 6-8 weeks.
+  •  Group III (5W-40, 5W-30, 0W-20) is the most volatile and entirely imported. Consider hedging 30-60 days of base oil inventory to protect Super Premium pricing from cost shocks.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A77:H77"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2580,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4528,7 +4632,6 @@
         <v/>
       </c>
     </row>
-    <row r="58"/>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="31" t="inlineStr">
         <is>
@@ -4536,13 +4639,74 @@
         </is>
       </c>
     </row>
+    <row r="61" ht="10" customHeight="1"/>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="78" customHeight="1">
+      <c r="A63" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Takes the final recommended list price from the weighted synthesis (Summary sheet) as the starting point.
+  •  Applies a structured discount cascade for each trade channel: Retail Pump = 0%, Workshop = -12%, Distributor = -15%, Fleet Contract = -20%.
+  •  Formula: Channel Price = List Price x (1 - Discount%)
+  •  The fleet contract price is the critical floor: it must never fall below the F4 cost waterfall floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="5" customHeight="1"/>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="156" customHeight="1">
+      <c r="A66" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Different trade channels have fundamentally different cost structures, volume commitments, and credit terms. A single price for all channels either overcharges workshops (losing trade) or undercharges fleet (losing margin).
+  •  Workshop -12%: they stock product, drive recommendations at service, but have no volume commitment. 12% is the minimum trade allowance to secure shelf placement and mechanic recommendation.
+  •  Distributor -15%: they take inventory risk, provide credit to dealers, manage last-mile logistics. 15% covers their operating costs and provides a viable business model.
+  •  Fleet -20%: they commit to annual volumes and provide predictable revenue, but negotiate aggressively and pay in 45-90 day cycles. 20% compensates for working capital cost and volume commitment.
+  •  A structured discount matrix prevents channel conflict: each account type knows their price and cannot arbitrage because the discount is tied to account type, not transaction size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="5" customHeight="1"/>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="130" customHeight="1">
+      <c r="A69" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Critical constraint: Fleet contract price (list x 0.80) must always exceed the F4 pocket price floor. If not, PSO is subsidising fleet customers from its own margin - unsustainable.
+  •  No channel should receive more than 20% off list without board-level approval. Any 'special deal' deeper than fleet discount erodes the entire price architecture.
+  •  Workshops are PSO's most strategic brand advocacy channel. The 12% discount is a relationship investment. Consider tiering: 12% standard, 14% for top-volume workshops, 16% for PSO-branded workshop partners.
+  •  Fleet contracts must be reviewed annually against the UPDATED synthesis price, not the prior year's list. If list prices rise 8% due to base oil inflation but fleet contracts are locked at prior year list, PSO absorbs the entire cost increase at its most margin-dilutive channel.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
     <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22685,7 +22849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -24557,7 +24721,6 @@
         <v/>
       </c>
     </row>
-    <row r="65"/>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
@@ -24565,13 +24728,73 @@
         </is>
       </c>
     </row>
+    <row r="68" ht="10" customHeight="1"/>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="91" customHeight="1">
+      <c r="A70" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Identifies the Shell tier equivalent for each PSO brand: Carient Ultra = Shell Helix Ultra (Super Premium), Carient Plus = ZIC X7/Total Quartz 9000 (Mainstream), Carient SPRO = Kixx G1 (Economy), etc.
+  •  Pulls the Daraz.pk median price/L for that Shell benchmark brand x grade combination from the competitor dataset.
+  •  Applies a PSO brand-perception discount: 8% for Super Premium, 6% Premium, 4% Mainstream, 2% Economy.
+  •  Formula: F1 Price = Shell_Tier_Median x (1 - Brand_Discount%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="5" customHeight="1"/>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="104" customHeight="1">
+      <c r="A73" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Shell is the cognitive price anchor in Pakistan's lubricants market. Consumers use Shell prices as a mental reference when evaluating any other brand, even if they do not realise it.
+  •  Pricing relative to Shell gives PSO a clear, defensible price story at the pump: 'same quality tier, better value.' This is easier to communicate than abstract per-litre comparisons.
+  •  The brand discount is NOT a permanent feature. It reflects today's gap in awareness and OEM approval depth. In markets where PSO has invested in workshops and A&amp;P, the effective gap is already closer to 2-3%.
+  •  Using the Shell MEDIAN (not Shell minimum) avoids being dragged down by short-term Shell promotional prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="5" customHeight="1"/>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="130" customHeight="1">
+      <c r="A76" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  As PSO brand equity grows through OEM approvals and ATL/BTL investment, the discount should narrow: Super Premium target is 3-4% below Shell by 2028, not 8%. Each 1% narrowing on Carient Ultra alone recovers approximately Rs 30-35/L in margin.
+  •  If Shell raises prices due to base oil cost pressures, PSO has immediate cover to follow: the percentage gap is maintained, so the absolute price difference actually grows, reinforcing 'best value.'
+  •  For Carient Ultra 0W-20 and 5W-30, the 8% discount may already be too deep given product quality. Consider narrowing to 5% in FY26 and redirecting recovered margin into workshop visibility programmes.
+  •  Monitor Shell pricing quarterly via the Daraz.pk scrape. Any Shell price movement triggers an immediate F1 recalculation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
+    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A75:H75"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24584,7 +24807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -26858,11 +27081,71 @@
         <v/>
       </c>
     </row>
+    <row r="78" ht="10" customHeight="1"/>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="91" customHeight="1">
+      <c r="A80" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Collects all non-PSO Daraz.pk listings for each grade x pack combination from the scraped dataset.
+  •  Computes the market median (50th percentile price per litre): the price at which half the competitors charge more and half charge less.
+  •  Positions PSO at exactly 3% below median: F2 = Market_Median x 0.97.
+  •  When fewer than 3 exact-pack listings exist, scope widens to all packs for that grade (flagged as 'Grade-wide' in the Scope column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="5" customHeight="1"/>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="117" customHeight="1">
+      <c r="A83" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  The market median is the most transparent benchmark: directly observable by any buyer comparing options online or in a workshop. It cannot be disputed.
+  •  3% below median (not 20% below) avoids the 'cheap brand' perception trap. FMCG research shows extreme discounting signals inferior quality more than value. PSO should be 'better value,' not 'cheap.'
+  •  Being 3% below median means PSO wins the tie-break when a buyer compares two similar-spec products at the same quality level: same spec, lower price, wins the shelf.
+  •  F2 carries the highest weight (30%) because it is the most current, market-facing signal and automatically absorbs competitor price movements without requiring model recalibration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="5" customHeight="1"/>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="117" customHeight="1">
+      <c r="A86" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Recalculate F2 quarterly using fresh Daraz scrape data. If competitor prices rise due to base oil pressures, F2 will show PSO can raise prices without losing competitive position.
+  •  The 3% discount is a policy choice. If PSO builds stronger brand equity, reduce it to 1-2%, capturing significant margin without volume loss. A 1% change on a 45-SKU range is material.
+  •  For 'Grade-wide' scope SKUs, the F2 result is less reliable. Prioritise getting pack-specific competitor data before finalising list prices for those SKUs.
+  •  F2 sets the baseline for both F3 (pack architecture) and F6 (geographic). An error in F2 propagates downstream: data quality in the competitor scrape is the single most important input to this model.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="10">
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A83:G83"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A85:G85"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26875,7 +27158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -28725,12 +29008,72 @@
         <v/>
       </c>
     </row>
+    <row r="76" ht="10" customHeight="1"/>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="104" customHeight="1">
+      <c r="A78" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Designates the 4L pack as the anchor (multiplier = 1.00x). All other pack sizes carry a multiplier relative to the 4L anchor price per litre.
+  •  The 4L market median (from competitor data for each grade) is the anchor price/L.
+  •  Each pack size price = 4L anchor x PPA multiplier. Example: 1L pack = 4L anchor x 1.40 (40% per-litre premium).
+  •  Multipliers are derived from international retail lubricants practice: smaller packs carry a convenience premium; larger packs carry a bulk discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="5" customHeight="1"/>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="117" customHeight="1">
+      <c r="A81" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Without a structured PPA, brands accidentally price 1L packs lower per litre than 3L packs (or vice versa), confusing price-aware buyers who calculate unit costs.
+  •  The 1L premium (40% above 4L per litre) is justified by: single engine-change convenience, retail display slot cost, impulse-purchase pricing psychology, and high turnover at petrol station forecourts.
+  •  A consistent price ladder prevents pack cannibalism: if 3L packs were priced at par with 4L per litre, buyers would always choose 3L, destroying 4L volumes and margin.
+  •  PSO's range spans 1L to 4L across the same brand/grade. Buyers who visit multiple channels compare cross-pack, and inconsistency destroys credibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="5" customHeight="1"/>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="117" customHeight="1">
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  The biggest revenue opportunity is the 1L PCMO pack at petrol stations, where buyers are least price-sensitive and most convenience-driven. The 40% per-litre premium is fully justifiable and should be enforced.
+  •  Review current 1L and 3L price points against the PPA ladder. The next list price revision is the right moment to re-anchor the entire range. Do not introduce mid-cycle exceptions.
+  •  Any new pack size launch (e.g., 800ml sachet) must have its PPA multiplier defined BEFORE launch. Without pre-setting the multiplier, the new pack will almost certainly be mispriced relative to the range.
+  •  For MCO (motorcycle oil), the 1L pack dominates sales. The 1.40x multiplier should be enforced here since MCO buyers are highly brand-loyal once a workshop mechanic recommends a product.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
+    <mergeCell ref="A84:G84"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A80:G80"/>
     <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A83:G83"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A78:G78"/>
     <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A81:G81"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28743,7 +29086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -31394,7 +31737,6 @@
         <v/>
       </c>
     </row>
-    <row r="81"/>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="31" t="inlineStr">
         <is>
@@ -31402,14 +31744,75 @@
         </is>
       </c>
     </row>
+    <row r="84" ht="10" customHeight="1"/>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="117" customHeight="1">
+      <c r="A86" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Builds the minimum viable price from cost structure upward, not downward from the market.
+  •  Step 1 - Cost build-up: Base oil import parity (Group I Rs 280/L, II Rs 420/L, III Rs 680/L) + Additive package (grade-specific) + Packaging (per-litre by pack size) = Total Manufacturing Cost.
+  •  Step 2 - Pocket price floor: Total Cost / (1 - Target Margin%). Targets: 45% Super Premium, 38% Premium, 30% Mainstream, 22% Economy. This is the minimum price that covers PSO's cost after all deductions.
+  •  Step 3 - List price floor: Pocket Price Floor / (1 - 20% Fleet Discount). Fleet is the deepest channel, so the list price must cover this to maintain margin everywhere.
+  •  F4 is a hard floor: if the weighted synthesis falls below F4, the recommendation is raised to F4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="5" customHeight="1"/>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="117" customHeight="1">
+      <c r="A89" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  The McKinsey Price Waterfall reveals how revenue 'leaks' from list price to the price that actually reaches PSO's P&amp;L ('pocket price'). Without this, individually small concessions destroy profitability collectively.
+  •  PSO's fleet channel is especially exposed: 20% off a list price set too low means PSO is subsidising fleet customers' engine oil from its own margin - an unsustainable practice.
+  •  The target margins (45% Super Premium to 22% Economy) reflect international lubricant industry norms adjusted for Pakistan's distribution structure, dealer margins, and working capital costs.
+  •  F4 also sets the minimum for fleet negotiation. Any fleet deal deeper than 20% off list requires explicit board approval because it breaches the pocket price floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="5" customHeight="1"/>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="130" customHeight="1">
+      <c r="A92" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  F4 fires most often for economy-tier HDEO (20W-50, 15W-40 mineral) where Korean/Chinese imports on Daraz drive market prices below PSO's cost floor. Do NOT match these prices.
+  •  Instead of cutting price below F4: (a) exit commodity packs where margin is structurally impossible, (b) reposition to 'value premium' with better packaging and communication, or (c) explore private-label manufacturing for fleet-only packs at different cost structure.
+  •  If F4 floor &gt; F7 floor for any grade, the margin target is correctly set above the pure cost floor - good. If F4 floor &lt; F7 floor, the margin assumption is too low and needs upward revision.
+  •  Re-run F4 whenever base oil import prices shift more than 10% - approximately every 6 months in a stable environment, more frequently during crude oil price shocks.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
+    <mergeCell ref="A92:L92"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A86:L86"/>
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A85:L85"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A89:L89"/>
+    <mergeCell ref="A88:L88"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A91:L91"/>
     <mergeCell ref="A34:L34"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
@@ -31423,7 +31826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -33290,11 +33693,71 @@
         <v/>
       </c>
     </row>
+    <row r="69" ht="10" customHeight="1"/>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="104" customHeight="1">
+      <c r="A71" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Anchors to the economy-tier (Kixx/Kixx G1) Daraz.pk median for each grade as the 'floor' baseline - what the same viscosity grade costs with the minimum viable API specification.
+  •  Applies an API/ACEA specification uplift based on PSO's tier: +28% for API SP fully synthetic, +18% for API SN+ semi-synthetic, +8% for API SN mineral, 0% for economy.
+  •  Formula: F5 Price = Economy_Baseline x (1 + Spec_Uplift%)
+  •  Uplift percentages are derived from international market research on OEM approval premiums in comparable emerging markets (India, Vietnam, Indonesia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="5" customHeight="1"/>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="143" customHeight="1">
+      <c r="A74" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Engine oil pricing must reflect specification level, not just viscosity grade. A 5W-40 API SP (fully synthetic) has fundamentally different chemistry, manufacturing cost, and engine protection vs a 5W-40 API SN mineral.
+  •  In Pakistan, pump attendants and workshop mechanics rarely explain spec differences. F5 sets the price SIGNAL that communicates quality: consumers learn to associate higher price with higher spec, even without reading the API label.
+  •  F5 is weighted at only 10% because spec literacy in Pakistan is still developing. As car parc modernises (more Euro-4/5 engines, more turbo/hybrid vehicles requiring SP/SN+), the spec premium will become more important and the weight should increase.
+  •  F5 also prevents underpricing of premium products: Carient Ultra 5W-40 (API SP) should never approach Kixx G1 5W-40 (API SN) pricing, regardless of competitive pressure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="5" customHeight="1"/>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="130" customHeight="1">
+      <c r="A77" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Investing in OEM approvals (VW 504.00, BMW Longlife-04, Toyota WS) directly increases the justifiable spec premium from 28% toward 35-40% for those specific SKUs. A single major OEM approval generates years of pricing power.
+  •  For economy HDEO (DEO 3000, Dieselube), the F5 uplift is 0% - these compete purely on price. Any price above the F5 baseline in the economy tier must be supported by brand or distribution advantages, not spec.
+  •  Monitor the economy baseline (Kixx pricing) closely. If Korean brands discount aggressively, the F5 baseline drops and PSO's spec premium erodes unless parallel brand investment is maintained.
+  •  Consider displaying API specification prominently on packaging and POS materials at petrol stations. Consumers who understand spec buy on spec, not just on price - this shifts F5 weight from 10% toward 20%.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A77:G77"/>
     <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A76:G76"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A73:G73"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A21:I21"/>
   </mergeCells>
@@ -33308,7 +33771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -35643,7 +36106,6 @@
         <v/>
       </c>
     </row>
-    <row r="63"/>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
@@ -35651,13 +36113,73 @@
         </is>
       </c>
     </row>
+    <row r="66" ht="10" customHeight="1"/>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="104" customHeight="1">
+      <c r="A68" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Uses PSO's own FY25 lubricants volume data (Lubes Data Final.xlsx) to compute regional YoY growth signals - the percentage difference in volume growth between each region and the national average.
+  •  Regions growing faster than the national average can support a price premium (e.g., Central DEO: +5%). Declining regions require a discount to defend volume (North MCO: -8%).
+  •  Formula: Regional Price = F2_National_Price x (1 + Regional_Signal%)
+  •  South (Karachi/Hyderabad) is the national baseline (0% adjustment). Adjustments are implemented as quarterly promotional price variations, NOT permanent list price changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="5" customHeight="1"/>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="36" t="inlineStr">
+        <is>
+          <t>RATIONALE  —  Why this framework is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="117" customHeight="1">
+      <c r="A71" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  Pakistan's lubricants market is deeply regional: Central Punjab drives HDEO (agricultural/transport), Karachi dominates PCMO, KPK/Northern corridor has distinct MCO patterns tied to two-wheeler density.
+  •  A flat national price leaves revenue on the table in strong-growth regions (where demand is relatively inelastic) and loses volume in weak regions (where buyers switch to cheaper local alternatives).
+  •  Geographic pricing is standard practice for CPG and lubricants companies in South Asia. Castrol, Shell, and Total all maintain regional trade price lists in Pakistan.
+  •  Using PSO's own volume data (not external estimates) makes the signal accurate and tied to PSO's distribution reality - it reflects where PSO is genuinely growing or losing ground.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="5" customHeight="1"/>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="38" t="inlineStr">
+        <is>
+          <t>IMPLICATIONS  —  What this means for PSO pricing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="117" customHeight="1">
+      <c r="A74" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  •  For HDEO in Central Punjab (+5%): this translates to Rs 75-90/L higher price on a 15W-40 4L pack. Recoverable through regional promotional pricing without disturbing the national list.
+  •  For MCO in North (-8%): this is a defensive measure. North MCO decline suggests PSO is losing to local blenders or two-wheeler brand partnerships. Pricing alone will not recover volume - conduct a distribution audit.
+  •  Grey market risk: if the South-to-North price gap on the same SKU exceeds Rs 50-70/L, distributors will buy cheap in South and sell in North. Cap regional variation at 5% on any high-volume SKU.
+  •  Update regional signals every 6 months using the latest PSO sales data. The FY25 data in this workbook will be stale by Q3 FY26 and must be refreshed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="11">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A74:K74"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="A71:K71"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A64:J64"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
